--- a/docs/tohopmon.xlsx
+++ b/docs/tohopmon.xlsx
@@ -1455,7 +1455,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1515,13 +1515,6 @@
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1977,28 +1970,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2007,118 +2003,115 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2485,7 +2478,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H1468"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.6" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="7.16666666666667" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
